--- a/docs/downloads/Stage 4 - Design.xlsx
+++ b/docs/downloads/Stage 4 - Design.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scope-to-Node Mapping" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="State Schema" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Node Specifications" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HIL Interaction Design" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Error Handling" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope-to-Action Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory Schema" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Specifications" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIL Interaction Design" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error Handling" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Graph Node</t>
+          <t>Flow Action</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -529,21 +529,21 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rule 1 (AUTOMATE → node) + Rule 4 (group tightly coupled steps)</t>
+          <t>Rule 1 (AUTOMATE → action) + Rule 4 (group tightly coupled steps)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>All four data retrieval steps (1-4) share the same logic pattern: API call with account_id + quarter date range. Different data sources but identical node behavior — call API, store result in state. Grouping into one node keeps the graph topology simple while internal parallelism handles concurrency.</t>
+          <t>All four data retrieval steps (1-4) share the same logic pattern: API call with account_id + quarter date range. Different data sources but identical action behaviour — call API, store result in memory. Grouping into one action keeps the flow structure simple while internal parallelism handles concurrency.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The four API calls within this node are independent and can be parallelised internally using async calls or Send()</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1">
+          <t>The four API calls within this action are independent and can be parallelised internally using async calls or the platform's fan-out primitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="105" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -571,12 +571,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Same logic pattern as Step 1: API call with account_id + date range. The tool differs (Support API vs CRM API) but the node behavior is identical — retrieve data and store in state. No reason to create a separate node for each data source when the pattern is the same.</t>
+          <t>Same logic pattern as Step 1: API call with account_id + date range. The tool differs (Support API vs CRM API) but the action behaviour is identical — retrieve data and store in memory. No reason to create a separate action for each data source when the pattern is the same.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>If the support API returns paginated results the node handles pagination internally</t>
+          <t>If the support API returns paginated results the action handles pagination internally</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Same logic pattern as Steps 1-2: API call with account_id + date range. Usage data API wrapper returns a single dict of metrics. Grouping with other retrieval steps avoids a graph with four sequential data-fetch nodes that could be one.</t>
+          <t>Same logic pattern as Steps 1-2: API call with account_id + date range. Usage data API wrapper returns a single dict of metrics. Grouping with other retrieval steps avoids a flow with four sequential data-fetch actions that could be one.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Same logic pattern as Steps 1-3: API call with account_id + date range. Slack search returns a list of thread dicts. Completes the data retrieval group — all four sources are fetched by one node with four internal tool calls.</t>
+          <t>Same logic pattern as Steps 1-3: API call with account_id + date range. Slack search returns a list of thread dicts. Completes the data retrieval group — all four sources are fetched by one action with four internal tool calls.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Slack threads use Annotated[list[dict] with operator.add] reducer in state to support potential future fan-out</t>
+          <t>Slack threads use an append reducer in memory to support potential future fan-out</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Steps 5-7 each have HIL elements (sentiment validation / ticket interpretation / usage context) but the human reviews related dimensions of the same account. Presenting all three analyses together in one interrupt is faster and produces better feedback — the reviewer can cross-reference findings across dimensions. The sentiment review merges into the analysis checkpoint rather than being its own interrupt.</t>
+          <t>Steps 5-7 each have HIL elements (sentiment validation / ticket interpretation / usage context) but the human reviews related dimensions of the same account. Presenting all three analyses together in one HIL checkpoint is faster and produces better feedback — the reviewer can cross-reference findings across dimensions. The sentiment review merges into the analysis checkpoint rather than being its own checkpoint.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>The HIL review for this step is deferred to the hil_review_analysis node which surfaces all three analyses together</t>
+          <t>The HIL review for this step is deferred to the hil_review_analysis action which surfaces all three analyses together</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>SLA thresholds and scoring criteria come from an external scoring rubric config file — not hardcoded in the node</t>
+          <t>SLA thresholds and scoring criteria come from an external scoring rubric config file — not hardcoded in the action</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>This node is the consolidated HIL checkpoint for Steps 5-7. Rather than three separate interrupts (one per analysis dimension) the graph pauses once and surfaces all three analyses together. The reviewer gets full context to cross-reference findings and can correct any dimension in a single interaction. This eliminates context-switching overhead and produces higher-quality feedback.</t>
+          <t>This action is the consolidated HIL checkpoint for Steps 5-7. Rather than three separate checkpoints (one per analysis dimension) the flow pauses once and surfaces all three analyses together. The reviewer gets full context to cross-reference findings and can correct any dimension in a single interaction. This eliminates context-switching overhead and produces higher-quality feedback.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Human corrections from hil_review_analysis flow forward via analysis_human_feedback in state so synthesise operates on vetted data</t>
+          <t>Human corrections from hil_review_analysis flow forward via analysis_human_feedback in memory so synthesise operates on vetted data</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Same reasoning as Step 8: the health score is derived from analysis outputs the human has already confirmed. The scoring framework (Green/Amber/Red with defined thresholds) is deterministic given validated inputs. An additional interrupt here would add overhead without meaningfully improving accuracy since the report review checkpoint catches scoring errors.</t>
+          <t>Same reasoning as Step 8: the health score is derived from analysis outputs the human has already confirmed. The scoring framework (Green/Amber/Red with defined thresholds) is deterministic given validated inputs. An additional HIL checkpoint here would add overhead without meaningfully improving accuracy since the report review checkpoint catches scoring errors.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Split boundary step: report drafting is automated (LLM fills a structured template with sections for each health dimension). The HIL review component is consolidated with Step 11's review into a single hil_review_report checkpoint. Steps 10 and 11 are grouped into one node because they share the same tool (LLM) and produce a single deliverable package (report + summary).</t>
+          <t>Split boundary step: report drafting is automated (LLM fills a structured template with sections for each health dimension). The HIL review component is consolidated with Step 11's review into a single hil_review_report checkpoint. Steps 10 and 11 are grouped into one action because they share the same tool (LLM) and produce a single deliverable package (report + summary).</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Same pattern as Step 10: exec summary generation is automated (LLM produces a 3-5 sentence summary from the completed report). The HIL review is consolidated into hil_review_report. Grouping with Step 10 is natural — the exec summary is derived from the report so they share inputs and are produced in sequence within the same node.</t>
+          <t>Same pattern as Step 10: exec summary generation is automated (LLM produces a 3-5 sentence summary from the completed report). The HIL review is consolidated into hil_review_report. Grouping with Step 10 is natural — the exec summary is derived from the report so they share inputs and are produced in sequence within the same action.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Rule 2 (HIL → interrupt node) + Consolidation Principle 1 (merge related reviews)</t>
+          <t>Rule 2 (HIL → HIL checkpoint action) + Consolidation Principle 1 (merge related reviews)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>This node is the consolidated HIL checkpoint for the report package (Steps 10-11). The human reviews the complete deliverable — full report and exec summary — in a single interaction. Uses Feedback-as-Control-Flow pattern because the human can approve / revise (report only) / rework (re-run analysis). Each decision routes to a different node.</t>
+          <t>This action is the consolidated HIL checkpoint for the report package (Steps 10-11). The human reviews the complete deliverable — full report and exec summary — in a single interaction. Uses Feedback-as-Control-Flow pattern because the human can approve / revise (report only) / rework (re-run analysis). Each decision routes to a different action.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Outside graph</t>
+          <t>Outside flow</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Rule 3 (MANUAL steps are outside the graph)</t>
+          <t>Rule 3 (MANUAL steps are outside the flow)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MANUAL steps happen after the graph completes. The graph ends when hil_review_report approves the output. Final edits / distribution list decisions / the actual send all happen outside graph.invoke(). The graph boundary ends at the last point where the agent adds value.</t>
+          <t>MANUAL steps happen after the flow completes. The flow ends when hil_review_report approves the output. Final edits / distribution list decisions / the actual send all happen outside the flow invocation. The flow boundary ends at the last point where the agent adds value.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1084,11 +1084,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.3" customWidth="1" min="1" max="1"/>
-    <col width="38.5" customWidth="1" min="2" max="2"/>
+    <col width="29.7" customWidth="1" min="2" max="2"/>
     <col width="15.4" customWidth="1" min="3" max="3"/>
-    <col width="28.6" customWidth="1" min="4" max="4"/>
+    <col width="30.8" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="35.2" customWidth="1" min="6" max="6"/>
+    <col width="28.6" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Source (which node writes)</t>
+          <t>Source (which action writes)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Consumed By (which nodes read)</t>
+          <t>Consumed By (which actions read)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Caller (graph invocation)</t>
+          <t>Caller (flow invocation)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Required input — the caller must supply this when invoking the graph</t>
+          <t>Required input — the caller must supply this when invoking the flow</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Caller (graph invocation)</t>
+          <t>Caller (flow invocation)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Caller (graph invocation)</t>
+          <t>Caller (flow invocation)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Annotated[list[dict], operator.add]</t>
+          <t>list[dict] (append reducer)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>operator.add (list accumulation)</t>
+          <t>append (list accumulation)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Reducer supports future fan-out if data gathering is split into parallel sub-nodes. Each ticket dict contains fields like severity / status / created_date / resolution_time / CSAT.</t>
+          <t>Reducer supports future fan-out if data gathering is split into parallel sub-actions. Each ticket dict contains fields like severity / status / created_date / resolution_time / CSAT.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Annotated[list[dict], operator.add]</t>
+          <t>list[dict] (append reducer)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>operator.add (list accumulation)</t>
+          <t>append (list accumulation)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Optional[str]</t>
+          <t>str (optional)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Feedback-as-Context pattern. None on first pass. When present the synthesise node's prompt injects this as additional context. On rework passes analyse_health also reads this to understand prior corrections.</t>
+          <t>Feedback-as-Context pattern. None on first pass. When present the synthesise action's prompt injects this as additional context. On rework passes analyse_health also reads this to understand prior corrections.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Optional[str]</t>
+          <t>str (optional)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Written only when report_review_decision = 'revise'. The generate_report node includes these instructions in its prompt on revision passes.</t>
+          <t>Written only when report_review_decision = 'revise'. The generate_report action includes these instructions in its prompt on revision passes.</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Optional[str]</t>
+          <t>str (optional)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Optional[str]</t>
+          <t>str (optional)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>HIL checkpoint 2: structured decision determining graph routing</t>
+          <t>HIL checkpoint 2: structured decision determining flow routing</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Constrained values: 'approved' | 'revise' | 'rework'. The routing function reads this field and returns the target node. ValueError raised on unrecognised values to prevent silent misrouting.</t>
+          <t>Constrained values: 'approved' | 'revise' | 'rework'. The routing function reads this field and returns the target action. An error is raised on unrecognised values to prevent silent misrouting.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Node Name</t>
+          <t>Action Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Node Type</t>
+          <t>Action Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Input State Fields</t>
+          <t>Input Memory Fields</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Output State Fields</t>
+          <t>Output Memory Fields</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. Read account_id and quarter from state. 2. Construct date range from quarter value. 3. Call CRM API wrapper with account_id to retrieve account metadata (ARR / contract dates / tier / key contacts). 4. Call Support API wrapper with account_id and date range to retrieve ticket records (handle pagination if results span multiple pages). 5. Call Usage data API wrapper with account_id and date range to retrieve product metrics (DAU/MAU / feature adoption / API error rates). 6. Call Slack search wrapper with account_id and date range to retrieve relevant customer channel threads. 7. Store each API response in the corresponding state field. All four API calls are independent and should be parallelised internally using async calls.</t>
+          <t>1. Read account_id and quarter from memory. 2. Construct date range from quarter value. 3. Call CRM API wrapper with account_id to retrieve account metadata (ARR / contract dates / tier / key contacts). 4. Call Support API wrapper with account_id and date range to retrieve ticket records (handle pagination if results span multiple pages). 5. Call Usage data API wrapper with account_id and date range to retrieve product metrics (DAU/MAU / feature adoption / API error rates). 6. Call Slack search wrapper with account_id and date range to retrieve relevant customer channel threads. 7. Store each API response in the corresponding memory field. All four API calls are independent and should be parallelised internally using async calls.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N/A — this node makes no LLM calls. It performs deterministic data retrieval from four external APIs.</t>
+          <t>N/A — this action makes no LLM calls. It performs deterministic data retrieval from four external APIs.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>If any data source API call fails (HTTP error / timeout / authentication error): store an error marker dict (e.g. {error: true / source: 'CRM API' / reason: 'HTTP 503 timeout'}) in the relevant state field and continue with remaining sources. Do not abort the graph — downstream nodes handle partial data. If a source returns an empty result set: store the empty result (not an error marker) — empty data is a valid state that analyse_health handles separately from errors.</t>
+          <t>If any data source API call fails (HTTP error / timeout / authentication error): store an error marker dict (e.g. {error: true / source: 'CRM API' / reason: 'HTTP 503 timeout'}) in the relevant memory field and continue with remaining sources. Do not abort the flow — downstream actions handle partial data. If a source returns an empty result set: store the empty result (not an error marker) — empty data is a valid value that analyse_health handles separately from errors.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>The four API calls can be parallelised internally. This keeps the graph topology simple (one node) while still getting concurrency benefits. Use fan-out at the graph level only when parallel branches have different logic not just different data sources.</t>
+          <t>The four API calls can be parallelised internally. This keeps the flow structure simple (one action) while still getting concurrency benefits. Use fan-out at the flow level only when parallel branches have different logic not just different data sources.</t>
         </is>
       </c>
     </row>
@@ -2112,22 +2112,22 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>LLM (Claude) — three separate calls, one per analysis dimension</t>
+          <t>LLM — three separate calls, one per analysis dimension</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. Check each upstream data field for error markers. For any field containing an error marker: skip that dimension and record a gap (score: 'Unknown') rather than sending bad data to the LLM. 2. Ticket analysis: load raw ticket data from tickets state field. Calculate volume trends / severity distribution / MTTR vs SLA targets / CSAT trends. Pass computed metrics and raw data to LLM for interpretation and scoring. 3. Usage analysis: load usage metrics from usage_data state field. Calculate DAU/MAU trends / feature adoption rates / API error rates. Pass to LLM for comparison against benchmarks and scoring. 4. Sentiment analysis: load Slack threads from slack_threads state field. Pass to LLM for theme identification / sentiment assessment / flagging specific threads for human attention. 5. On rework passes (when rework_instructions is present): include the reviewer's instructions as a focus-area section in all three prompts. 6. Store each analysis result in the corresponding state field. Each dimension runs independently — failure in one does not block others.</t>
+          <t>1. Check each upstream data field for error markers. For any field containing an error marker: skip that dimension and record a gap (score: 'Unknown') rather than sending bad data to the LLM. 2. Ticket analysis: load raw ticket data from tickets memory field. Calculate volume trends / severity distribution / MTTR vs SLA targets / CSAT trends. Pass computed metrics and raw data to LLM for interpretation and scoring. 3. Usage analysis: load usage metrics from usage_data memory field. Calculate DAU/MAU trends / feature adoption rates / API error rates. Pass to LLM for comparison against benchmarks and scoring. 4. Sentiment analysis: load Slack threads from slack_threads memory field. Pass to LLM for theme identification / sentiment assessment / flagging specific threads for human attention. 5. On rework passes (when rework_instructions is present): include the reviewer's instructions as a focus-area section in all three prompts. 6. Store each analysis result in the corresponding memory field. Each dimension runs independently — failure in one does not block others.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Three separate prompts — one per analysis dimension. Each receives account_name and quarter as account context. (1) Ticket analysis prompt: provide raw ticket data from tickets state field + SLA thresholds from sla_benchmarks section of scoring rubric config + account_tier from crm_data for tier-contextualised evaluation. Output format: JSON with keys {score: str / trend: str / volume_vs_previous_quarter: str / key_issues: [str] / sla_compliance: str / details: str}. (2) Usage analysis prompt: provide usage metrics from usage_data state field + adoption thresholds from adoption_benchmarks section of scoring rubric config. Output format: JSON with keys {score: str / trend: str / feature_adoption: str / details: str}. (3) Sentiment analysis prompt: provide Slack messages from slack_threads state field. No config section — sentiment assessed qualitatively from thread content. Output format: JSON with keys {score: str / summary: str / key_threads: [str]}. On rework passes all three prompts include rework_instructions as a focus-area section.</t>
+          <t>Three separate prompts — one per analysis dimension. Each receives account_name and quarter as account context. (1) Ticket analysis prompt: provide raw ticket data from tickets memory field + SLA thresholds from sla_benchmarks section of scoring rubric config + account_tier from crm_data for tier-contextualised evaluation. Output format: JSON with keys {score: str / trend: str / volume_vs_previous_quarter: str / key_issues: [str] / sla_compliance: str / details: str}. (2) Usage analysis prompt: provide usage metrics from usage_data memory field + adoption thresholds from adoption_benchmarks section of scoring rubric config. Output format: JSON with keys {score: str / trend: str / feature_adoption: str / details: str}. (3) Sentiment analysis prompt: provide Slack messages from slack_threads memory field. No config section — sentiment assessed qualitatively from thread content. Output format: JSON with keys {score: str / summary: str / key_threads: [str]}. On rework passes all three prompts include rework_instructions as a focus-area section.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>If an upstream data field contains an error marker: skip that dimension and record score as 'Unknown' — do not send error data to the LLM. If the LLM returns malformed JSON for any dimension: retry with a stricter format instruction (up to 2 retries per dimension). If retries exhausted: escalate via interrupt() with the failure context and raw data so the human can intervene. Each dimension fails independently — a parse failure in ticket analysis does not block usage or sentiment analysis.</t>
+          <t>If an upstream data field contains an error marker: skip that dimension and record score as 'Unknown' — do not send error data to the LLM. If the LLM returns malformed JSON for any dimension: retry with a stricter format instruction (up to 2 retries per dimension). If retries exhausted: escalate via an HIL checkpoint with the failure context and raw data so the human can intervene. Each dimension fails independently — a parse failure in ticket analysis does not block usage or sentiment analysis.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2169,22 +2169,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>None — uses interrupt() to pause execution</t>
+          <t>None — the HIL checkpoint pauses execution</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Format a summary of all three analyses (ticket_analysis / usage_analysis / sentiment_analysis) including scores / trends / key findings / evidence for each dimension. 2. Call interrupt() with the formatted summary payload. Execution pauses here. 3. When the human responds via Command(resume=&lt;feedback string&gt;): store the freeform input in analysis_human_feedback. 4. The raw analyses remain unchanged in state — preserving the audit trail of what the agent produced vs what the human corrected.</t>
+          <t>1. Format a summary of all three analyses (ticket_analysis / usage_analysis / sentiment_analysis) including scores / trends / key findings / evidence for each dimension. 2. Pause at the HIL checkpoint and surface the formatted summary payload to the reviewer. Execution pauses here. 3. When the human resumes the flow with their freeform feedback: store the input in analysis_human_feedback. 4. The raw analyses remain unchanged in memory — preserving the audit trail of what the agent produced vs what the human corrected.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>N/A — this node makes no LLM calls. It surfaces state data to the human and stores their response.</t>
+          <t>N/A — this action makes no LLM calls. It surfaces state data to the human and stores their response.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>State persists via LangGraph checkpointing. If the human does not respond execution pauses indefinitely and can be resumed later — no timeout crash. No data is lost during the pause.</t>
+          <t>Memory persists via the chosen framework's checkpointing layer. If the human does not respond execution pauses indefinitely and can be resumed later — no timeout crash. No data is lost during the pause.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Feedback-as-Context pattern: the human's input shapes what the synthesise node knows / not which node runs next. The interrupt payload should present analyses in a format optimised for review — not raw JSON but formatted scores / findings / evidence per dimension.</t>
+          <t>Feedback-as-Context pattern: the human's input shapes what the synthesise action knows / not which action runs next. The checkpoint payload should present analyses in a format optimised for review — not raw JSON but formatted scores / findings / evidence per dimension.</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LLM (Claude)</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Load all three analysis outputs from state (ticket_analysis / usage_analysis / sentiment_analysis). 2. Load human feedback from analysis_human_feedback (if present — may be None on first pass or if human confirmed without changes). 3. Load CRM contract context from crm_data (ARR / contract_end / renewal_date). 4. Load health_scoring section from scoring rubric config. 5. Pass all inputs to a single synthesis LLM prompt. 6. Parse the structured JSON response and store: risks / opportunities / health_score / health_justification in state. 7. Cross-reference findings with contract renewal timeline to surface time-sensitive risks.</t>
+          <t>1. Load all three analysis outputs from memory (ticket_analysis / usage_analysis / sentiment_analysis). 2. Load human feedback from analysis_human_feedback (if present — may be None on first pass or if human confirmed without changes). 3. Load CRM contract context from crm_data (ARR / contract_end / renewal_date). 4. Load health_scoring section from scoring rubric config. 5. Pass all inputs to a single synthesis LLM prompt. 6. Parse the structured JSON response and store: risks / opportunities / health_score / health_justification in memory. 7. Cross-reference findings with contract renewal timeline to surface time-sensitive risks.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>If the LLM returns malformed JSON: retry with a stricter format instruction (up to 2 retries). If retries exhausted: escalate via interrupt() with the available analysis data so the human can produce the synthesis manually. If upstream analysis dimensions have 'Unknown' scores (from data gaps the human did not override at the analysis checkpoint): include them as-is — the LLM is instructed to flag gaps rather than infer from absence.</t>
+          <t>If the LLM returns malformed JSON: retry with a stricter format instruction (up to 2 retries). If retries exhausted: escalate via an HIL checkpoint with the available analysis data so the human can produce the synthesis manually. If upstream analysis dimensions have 'Unknown' scores (from data gaps the human did not override at the analysis checkpoint): include them as-is — the LLM is instructed to flag gaps rather than infer from absence.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>LLM (Claude) — two calls: one for the report and one for the exec summary</t>
+          <t>LLM — two calls: one for the report and one for the exec summary</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. Load all analysis outputs / synthesis outputs / and CRM context from state. 2. On revision passes: load report_human_feedback and include as revision instructions. 3. Call LLM with a report generation prompt using a seven-section template (Account Overview / Ticket Health / Product Engagement / Sentiment / Risks &amp; Opportunities / Health Score / Recommended Actions). 4. Store the generated report in report_markdown. 5. Call LLM with an exec summary prompt — provide the completed report_markdown and ask for a 3-5 sentence plain text summary. 6. Store the summary in exec_summary.</t>
+          <t>1. Load all analysis outputs / synthesis outputs / and CRM context from memory. 2. On revision passes: load report_human_feedback and include as revision instructions. 3. Call LLM with a report generation prompt using a seven-section template (Account Overview / Ticket Health / Product Engagement / Sentiment / Risks &amp; Opportunities / Health Score / Recommended Actions). 4. Store the generated report in report_markdown. 5. Call LLM with an exec summary prompt — provide the completed report_markdown and ask for a 3-5 sentence plain text summary. 6. Store the summary in exec_summary.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Consolidates Scope Steps 10-11. The exec summary is generated after the report because it is derived from the completed report text. Two sequential LLM calls within the same node.</t>
+          <t>Consolidates Scope Steps 10-11. The exec summary is generated after the report because it is derived from the completed report text. Two sequential LLM calls within the same action.</t>
         </is>
       </c>
     </row>
@@ -2340,22 +2340,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>None — uses interrupt() to pause execution</t>
+          <t>None — the HIL checkpoint pauses execution</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Format the complete report package: report_markdown + exec_summary + health_score + risks + opportunities. 2. Call interrupt() with the formatted payload and explicit decision options (approved / revise / rework). Execution pauses here. 3. When the human responds via Command(resume={decision: str / instructions: str}): store the decision in report_review_decision. 4. Route the instructions to the correct state field based on the decision: if 'revise' → store instructions in report_human_feedback (read by generate_report on next pass). If 'rework' → store instructions in rework_instructions (read by analyse_health on next pass). If 'approved' → no instructions needed. 5. The routing function reads report_review_decision and returns the target node.</t>
+          <t>1. Format the complete report package: report_markdown + exec_summary + health_score + risks + opportunities. 2. Pause at the HIL checkpoint with the formatted payload and explicit decision options (approved / revise / rework). Execution pauses here. 3. When the human resumes the flow with a structured response {decision: str / instructions: str}: store the decision in report_review_decision. 4. Route the instructions to the correct memory field based on the decision: if 'revise' → store instructions in report_human_feedback (read by generate_report on next pass). If 'rework' → store instructions in rework_instructions (read by analyse_health on next pass). If 'approved' → no instructions needed. 5. The routing function reads report_review_decision and returns the target action.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>N/A — this node makes no LLM calls. It surfaces the report package to the human and processes their structured response.</t>
+          <t>N/A — this action makes no LLM calls. It surfaces the report package to the human and processes their structured response.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>State persists via LangGraph checkpointing — an unresponsive human does not crash the graph. Execution resumes whenever the human provides input. The routing function validates that the decision is one of 'approved' / 'revise' / 'rework' and raises ValueError on an unrecognised value / preventing silent misrouting to an undefined node.</t>
+          <t>Memory persists via the chosen framework's checkpointing layer — an unresponsive human does not crash the flow. Execution resumes whenever the human provides input. The routing function validates that the decision is one of 'approved' / 'revise' / 'rework' and raises an error on an unrecognised value / preventing silent misrouting to an undefined action.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Feedback-as-Control-Flow pattern: the human's decision determines which node runs next. The revise path re-runs only report generation; the rework path re-runs analysis and everything downstream. This gives the reviewer proportional control — minor wording issues use revise while fundamental analysis errors use rework.</t>
+          <t>Feedback-as-Control-Flow pattern: the human's decision determines which action runs next. The revise path re-runs only report generation; the rework path re-runs analysis and everything downstream. This gives the reviewer proportional control — minor wording issues use revise while fundamental analysis errors use rework.</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HIL Node Name</t>
+          <t>HIL Action Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>State Fields Written</t>
+          <t>Memory Fields Written</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Unconditional edge → synthesise. The graph always moves forward to synthesise regardless of what the human says. The human's input shapes what the synthesise node knows / not which node runs next.</t>
+          <t>Unconditional edge → synthesise. The flow always moves forward to synthesise regardless of what the human says. The human's input shapes what the synthesise action knows / not which action runs next.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The human reviews related dimensions of the same account together — presenting three separate interrupts for tickets / usage / and sentiment would force context-switching and prevent cross-referencing. Feedback-as-Context is correct because the human enriches the next node's reasoning (corrections flow into the synthesis prompt as additional context) without changing the graph's path. The synthesise node always runs after this checkpoint. An upstream validation here also enables Consolidation Principle 2: Steps 8-9 (synthesis) can be automated because the human has already confirmed the inputs.</t>
+          <t>The human reviews related dimensions of the same account together — presenting three separate HIL checkpoints for tickets / usage / and sentiment would force context-switching and prevent cross-referencing. Feedback-as-Context is correct because the human enriches the next action's reasoning (corrections flow into the synthesis prompt as additional context) without changing the flow's path. The synthesise action always runs after this checkpoint. An upstream validation here also enables Consolidation Principle 2: Steps 8-9 (synthesis) can be automated because the human has already confirmed the inputs.</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Complete report package: (1) Full report_markdown with all seven sections (Account Overview / Ticket Health / Product Engagement / Sentiment / Risks &amp; Opportunities / Health Score / Recommended Actions). (2) exec_summary — the 3-5 sentence executive summary. (3) health_score and health_justification displayed prominently. (4) risks and opportunities lists. The interrupt payload presents explicit decision options: approve / revise / rework — with descriptions of what each option does.</t>
+          <t>Complete report package: (1) Full report_markdown with all seven sections (Account Overview / Ticket Health / Product Engagement / Sentiment / Risks &amp; Opportunities / Health Score / Recommended Actions). (2) exec_summary — the 3-5 sentence executive summary. (3) health_score and health_justification displayed prominently. (4) risks and opportunities lists. The checkpoint payload presents explicit decision options: approve / revise / rework — with descriptions of what each option does.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Conditional edges based on report_review_decision: (1) 'approved' → END — the report is final and the graph completes. (2) 'revise' → generate_report — only the report is regenerated using report_human_feedback as revision instructions. Analysis and synthesis are preserved. (3) 'rework' → analyse_health — the analysis is re-run from scratch using rework_instructions as a focus-area guide. Synthesis and report generation also re-run downstream.</t>
+          <t>Conditional edges based on report_review_decision: (1) 'approved' → END — the report is final and the flow completes. (2) 'revise' → generate_report — only the report is regenerated using report_human_feedback as revision instructions. Analysis and synthesis are preserved. (3) 'rework' → analyse_health — the analysis is re-run from scratch using rework_instructions as a focus-area guide. Synthesis and report generation also re-run downstream.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>approved — the report meets quality standards and is ready for the MANUAL distribution step (Step 12 / outside graph). revise — the report has issues that can be fixed by regenerating the report text without changing the underlying analysis (e.g. tone / structure / missing detail). rework — the underlying analysis is flawed and needs to be re-run before a new report can be generated (e.g. a score is wrong / a key finding is missing / sentiment was misinterpreted).</t>
+          <t>approved — the report meets quality standards and is ready for the MANUAL distribution step (Step 12 / outside flow). revise — the report has issues that can be fixed by regenerating the report text without changing the underlying analysis (e.g. tone / structure / missing detail). rework — the underlying analysis is flawed and needs to be re-run before a new report can be generated (e.g. a score is wrong / a key finding is missing / sentiment was misinterpreted).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Which Nodes Are Affected</t>
+          <t>Which Actions Are Affected</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Store an error marker dict in the relevant state field — e.g. {error: true / source: 'Support API' / reason: 'HTTP 503 Service Unavailable' / timestamp: '2026-01-15T10:30:00Z'}. Continue gathering from remaining data sources. Do not retry at the gather_data level — API failures are typically not transient within the same execution window. The error marker propagates forward through the graph as a signal to downstream nodes.</t>
+          <t>Store an error marker dict in the relevant memory field — e.g. {error: true / source: 'Support API' / reason: 'HTTP 503 Service Unavailable' / timestamp: '2026-01-15T10:30:00Z'}. Continue gathering from remaining data sources. Do not retry at the gather_data level — API failures are typically not transient within the same execution window. The error marker propagates forward through the flow as a signal to downstream actions.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Default to graceful degradation. A report with one flagged data gap is more useful than no report at all. The error marker pattern preserves the specific failure reason so downstream nodes and human reviewers can assess the impact.</t>
+          <t>Default to graceful degradation. A report with one flagged data gap is more useful than no report at all. The error marker pattern preserves the specific failure reason so downstream actions and human reviewers can assess the impact.</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Retry with a stricter format instruction appended to the prompt — e.g. 'You MUST respond with valid JSON matching this exact schema: {schema}. Do not include any text outside the JSON object.' Up to 2 retries per failed call (3 total attempts). In analyse_health: each dimension retries independently — a parse failure in ticket analysis does not block usage or sentiment analysis. In synthesise: the entire synthesis retries since it produces a single integrated output. If all retries exhausted: escalate via interrupt() with the failure context (which node / which dimension / the raw LLM response / the expected schema) so the human can either fix the output manually or provide the structured data directly.</t>
+          <t>Retry with a stricter format instruction appended to the prompt — e.g. 'You MUST respond with valid JSON matching this exact schema: {schema}. Do not include any text outside the JSON object.' Up to 2 retries per failed call (3 total attempts). In analyse_health: each dimension retries independently — a parse failure in ticket analysis does not block usage or sentiment analysis. In synthesise: the entire synthesis retries since it produces a single integrated output. If all retries exhausted: escalate via an HIL checkpoint with the failure context (which action / which dimension / the raw LLM response / the expected schema) so the human can either fix the output manually or provide the structured data directly.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>If escalated in analyse_health: the human provides the analysis for that dimension manually — downstream nodes operate normally on human-provided data. If escalated in synthesise: the human produces the synthesis manually — generate_report operates normally. If a dimension in analyse_health permanently fails and is not escalated (edge case — should not happen with the escalation path): that dimension carries an error marker and the downstream impact follows the same pattern as 'Data source API failure'.</t>
+          <t>If escalated in analyse_health: the human provides the analysis for that dimension manually — downstream actions operate normally on human-provided data. If escalated in synthesise: the human produces the synthesis manually — generate_report operates normally. If a dimension in analyse_health permanently fails and is not escalated (edge case — should not happen with the escalation path): that dimension carries an error marker and the downstream impact follows the same pattern as 'Data source API failure'.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>hil_review_analysis: the human reviewer compares LLM-generated analyses against the raw data surfaced in the interrupt payload. Corrections flow into analysis_human_feedback and shape downstream synthesis. hil_review_report: the human reviewer evaluates the final report for unsupported claims. The revise path fixes report-level issues; the rework path re-runs analysis if the underlying interpretation is wrong.</t>
+          <t>hil_review_analysis: the human reviewer compares LLM-generated analyses against the raw data surfaced in the HIL checkpoint payload. Corrections flow into analysis_human_feedback and shape downstream synthesis. hil_review_report: the human reviewer evaluates the final report for unsupported claims. The revise path fixes report-level issues; the rework path re-runs analysis if the underlying interpretation is wrong.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Human does not respond to interrupt (reviewer unavailable)</t>
+          <t>Human does not respond at HIL checkpoint (reviewer unavailable)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Configurable timeout or indefinite wait — detected by the application layer monitoring graph execution duration. LangGraph itself does not timeout on interrupts — the graph simply pauses.</t>
+          <t>Configurable timeout or indefinite wait — detected by the application layer monitoring flow execution duration. Most agent frameworks do not timeout at an HIL checkpoint — the flow simply pauses.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Error marker and continue (state persistence via checkpointing)</t>
+          <t>Error marker and continue (memory persistence via checkpointing)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>State persists via LangGraph checkpointing. The graph pauses indefinitely at the interrupt point and can be resumed at any time when the human provides input via Command(resume=...). No data is lost during the pause. The application layer can optionally implement a notification system (e.g. send a reminder after 24 hours) but this is outside the graph's responsibility. No timeout crash — the graph simply waits.</t>
+          <t>Memory persists via the chosen framework's checkpointing layer. The flow pauses indefinitely at the HIL checkpoint and can be resumed at any time when the human provides input. No data is lost during the pause. The application layer can optionally implement a notification system (e.g. send a reminder after 24 hours) but this is outside the flow's responsibility. No timeout crash — the flow simply waits.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>No downstream impact until the human responds. All state is preserved exactly as it was when the interrupt was called. Execution resumes at the exact point it paused — the node picks up from after the interrupt() call and processes the human's input. Other graph executions (for different accounts) are not affected — each execution has its own checkpointed state.</t>
+          <t>No downstream impact until the human responds. All memory is preserved exactly as it was when the checkpoint paused. Execution resumes at the exact point it paused — the action picks up after the HIL checkpoint and processes the human's input. Other flow executions (for different accounts) are not affected — each execution has its own checkpointed memory.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LangGraph's checkpointing architecture means unresponsive humans are a non-issue for graph integrity. The concern is operational (SLA for report delivery) not technical (data loss or crashes). The application layer — not the graph — should handle operational concerns like reminder notifications and escalation to a backup reviewer.</t>
+          <t>The checkpointing architecture of most agent frameworks means unresponsive humans are a non-issue for flow integrity. The concern is operational (SLA for report delivery) not technical (data loss or crashes). The application layer — not the flow — should handle operational concerns like reminder notifications and escalation to a backup reviewer.</t>
         </is>
       </c>
     </row>
